--- a/data/trans_orig/P05B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05B-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la calidad percibida del medioambiente de su barrio en 2007</t>
+          <t>Población según la calidad percibida del medioambiente de su barrio en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15551</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39376</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47985</t>
+          <t>47590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78306</t>
+          <t>78304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75155</t>
+          <t>74371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114352</t>
+          <t>110555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>198444</t>
+          <t>199298</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>250393</t>
+          <t>251943</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>246389</t>
+          <t>246669</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>309482</t>
+          <t>310512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>458937</t>
+          <t>462713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>538499</t>
+          <t>541486</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>639518</t>
+          <t>639619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>700082</t>
+          <t>700476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>824942</t>
+          <t>819859</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>897565</t>
+          <t>893300</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1482875</t>
+          <t>1487675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1575702</t>
+          <t>1573863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87267</t>
+          <t>86158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124896</t>
+          <t>122766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93610</t>
+          <t>91866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134021</t>
+          <t>133392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189053</t>
+          <t>186232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>246655</t>
+          <t>244538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23140</t>
+          <t>22378</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,82 +1430,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9816</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17132</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>23125</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>14240</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>33483</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9816</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4880</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17354</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>23125</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>15016</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>35337</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47784</t>
+          <t>48595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45481</t>
+          <t>46910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77344</t>
+          <t>78321</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77496</t>
+          <t>76457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>117217</t>
+          <t>113079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285441</t>
+          <t>283056</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>350908</t>
+          <t>348206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>301246</t>
+          <t>302435</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>370366</t>
+          <t>366812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>606104</t>
+          <t>602581</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>693983</t>
+          <t>694114</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1116776</t>
+          <t>1116084</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1191896</t>
+          <t>1191417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>972822</t>
+          <t>981026</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1054331</t>
+          <t>1057475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2114779</t>
+          <t>2115352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2217506</t>
+          <t>2226483</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,89%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150317</t>
+          <t>150481</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203077</t>
+          <t>201062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145279</t>
+          <t>143007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193488</t>
+          <t>193298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307520</t>
+          <t>307956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>377615</t>
+          <t>376809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>13400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18840</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10047</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>25872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>16959</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38548</t>
+          <t>38480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103416</t>
+          <t>105512</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>146268</t>
+          <t>148818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81217</t>
+          <t>80015</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116446</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>193676</t>
+          <t>194522</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>247048</t>
+          <t>247059</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>304294</t>
+          <t>305672</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>355109</t>
+          <t>353628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>288558</t>
+          <t>288430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>332480</t>
+          <t>332395</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>611668</t>
+          <t>612477</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>672932</t>
+          <t>676181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61477</t>
+          <t>62098</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96525</t>
+          <t>94335</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35284</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61626</t>
+          <t>60492</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>105249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148144</t>
+          <t>149036</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33491</t>
+          <t>32611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12486</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>30036</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31124</t>
+          <t>30041</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56991</t>
+          <t>58166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>58566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93036</t>
+          <t>95655</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116870</t>
+          <t>116553</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>163127</t>
+          <t>160354</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>186355</t>
+          <t>185225</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>241382</t>
+          <t>243605</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>616984</t>
+          <t>621924</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>709963</t>
+          <t>712896</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>658784</t>
+          <t>657519</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>756055</t>
+          <t>752487</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1306870</t>
+          <t>1304224</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1440174</t>
+          <t>1437931</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2101105</t>
+          <t>2098637</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2206990</t>
+          <t>2206359</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2133817</t>
+          <t>2135263</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2243091</t>
+          <t>2246005</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4261901</t>
+          <t>4267314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4419779</t>
+          <t>4424225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>323548</t>
+          <t>318544</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>394242</t>
+          <t>391800</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>293599</t>
+          <t>293614</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>360756</t>
+          <t>361689</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>634305</t>
+          <t>635306</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>731274</t>
+          <t>733809</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la calidad percibida del medioambiente de su barrio en 2012</t>
+          <t>Población según la calidad percibida del medioambiente de su barrio en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16556</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>115381</t>
+          <t>114121</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159954</t>
+          <t>160337</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>178483</t>
+          <t>177583</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234155</t>
+          <t>231226</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>311329</t>
+          <t>309620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>380439</t>
+          <t>380172</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>697732</t>
+          <t>697645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>752970</t>
+          <t>754530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>948437</t>
+          <t>944799</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1014360</t>
+          <t>1009726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1659712</t>
+          <t>1664835</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1745770</t>
+          <t>1750506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76460</t>
+          <t>75997</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114918</t>
+          <t>113269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106019</t>
+          <t>103301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>148459</t>
+          <t>148081</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191605</t>
+          <t>190501</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>245568</t>
+          <t>248165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21888</t>
+          <t>19930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36441</t>
+          <t>36372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>21182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44377</t>
+          <t>44745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40942</t>
+          <t>39736</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72263</t>
+          <t>72739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>234756</t>
+          <t>238154</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>299997</t>
+          <t>298300</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>234297</t>
+          <t>232770</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>299405</t>
+          <t>299190</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>489512</t>
+          <t>485582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>577362</t>
+          <t>577689</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1393675</t>
+          <t>1393351</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1477082</t>
+          <t>1471606</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1236607</t>
+          <t>1236847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1318067</t>
+          <t>1314770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2651841</t>
+          <t>2655024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2765484</t>
+          <t>2764991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199330</t>
+          <t>198037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258124</t>
+          <t>256993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151401</t>
+          <t>153267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203188</t>
+          <t>205153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364712</t>
+          <t>365331</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>439510</t>
+          <t>441908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>48035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79549</t>
+          <t>78573</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58616</t>
+          <t>60057</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92430</t>
+          <t>93243</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117359</t>
+          <t>115413</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>164561</t>
+          <t>161621</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>318025</t>
+          <t>318553</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>362619</t>
+          <t>361453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>294957</t>
+          <t>294276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>337162</t>
+          <t>334601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>624939</t>
+          <t>627388</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>684692</t>
+          <t>686727</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46915</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79065</t>
+          <t>79576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>49716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81565</t>
+          <t>82234</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104963</t>
+          <t>103131</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>150611</t>
+          <t>148964</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24540</t>
+          <t>24814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>16898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31520</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59171</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35684</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65940</t>
+          <t>63296</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70855</t>
+          <t>72492</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>109860</t>
+          <t>112267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>426558</t>
+          <t>427257</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>510852</t>
+          <t>511713</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>500540</t>
+          <t>502678</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>590406</t>
+          <t>588502</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>951558</t>
+          <t>953818</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1072469</t>
+          <t>1075288</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2446994</t>
+          <t>2447027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2557295</t>
+          <t>2553742</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2515219</t>
+          <t>2516961</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2620879</t>
+          <t>2621762</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4997868</t>
+          <t>4995387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5151020</t>
+          <t>5142852</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>346329</t>
+          <t>345962</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>422098</t>
+          <t>424890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>331513</t>
+          <t>329593</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>405921</t>
+          <t>401985</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>694692</t>
+          <t>695716</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>799242</t>
+          <t>801385</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la calidad percibida del medioambiente de su barrio en 2016</t>
+          <t>Población según la calidad percibida del medioambiente de su barrio en 2016 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36247</t>
+          <t>35668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44512</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74035</t>
+          <t>73477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>109801</t>
+          <t>110141</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>106577</t>
+          <t>107348</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>151578</t>
+          <t>154946</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>189821</t>
+          <t>189861</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>249606</t>
+          <t>246087</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>434818</t>
+          <t>437339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>487203</t>
+          <t>488368</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>597463</t>
+          <t>598301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>661484</t>
+          <t>661010</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,47 +7040,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>60,59%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>66,94%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1090258</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1052866</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>1129421</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>62,65%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>60,5%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>66,99%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1090258</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1048997</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1130246</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>62,65%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>60,27%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,9%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168362</t>
+          <t>168472</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214307</t>
+          <t>213045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>181311</t>
+          <t>181238</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235992</t>
+          <t>235336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>359999</t>
+          <t>361810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>431229</t>
+          <t>428881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,82 +7348,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3917</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10377</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>13107</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>6942</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>22872</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3917</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9109</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>13107</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7013</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>22251</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12311</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30636</t>
+          <t>31644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51444</t>
+          <t>51910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42504</t>
+          <t>43652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72359</t>
+          <t>75951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>230138</t>
+          <t>228113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>290760</t>
+          <t>290227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221878</t>
+          <t>222369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>283939</t>
+          <t>284931</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>473307</t>
+          <t>471348</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>555998</t>
+          <t>558093</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1303148</t>
+          <t>1297743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1392916</t>
+          <t>1389962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1193556</t>
+          <t>1194550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1279912</t>
+          <t>1279469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2515949</t>
+          <t>2509979</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2639043</t>
+          <t>2640349</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>401255</t>
+          <t>397613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>476512</t>
+          <t>474442</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>410632</t>
+          <t>410885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>487755</t>
+          <t>487249</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>836766</t>
+          <t>833166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>946199</t>
+          <t>935646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -8015,97 +8015,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5085</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1254</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5085</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1254</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>7488</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>24219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>48931</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81792</t>
+          <t>81633</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50217</t>
+          <t>50146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79746</t>
+          <t>81154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>107525</t>
+          <t>108125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>152051</t>
+          <t>152899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>325757</t>
+          <t>327424</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>373000</t>
+          <t>372960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>331575</t>
+          <t>332873</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>374892</t>
+          <t>375937</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>671769</t>
+          <t>670143</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>736901</t>
+          <t>736220</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,23%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105019</t>
+          <t>105330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>145928</t>
+          <t>146979</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102776</t>
+          <t>104874</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>141427</t>
+          <t>142693</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219414</t>
+          <t>222782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>275097</t>
+          <t>279144</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19733</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28774</t>
+          <t>29252</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>23944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>48203</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52860</t>
+          <t>53132</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>86101</t>
+          <t>87148</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,47 +8860,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>103152</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>84041</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>123217</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>1,5%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>103152</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>83599</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>126230</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>376680</t>
+          <t>381081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>455639</t>
+          <t>456629</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>406946</t>
+          <t>405501</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>484615</t>
+          <t>485514</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>807822</t>
+          <t>804634</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>924612</t>
+          <t>917072</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2103939</t>
+          <t>2102274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2214859</t>
+          <t>2211854</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2166043</t>
+          <t>2160856</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2280093</t>
+          <t>2285398</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4299681</t>
+          <t>4292259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4470433</t>
+          <t>4454957</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699280</t>
+          <t>703169</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>804510</t>
+          <t>797776</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>728595</t>
+          <t>728211</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>827910</t>
+          <t>830912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1451949</t>
+          <t>1452110</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1593877</t>
+          <t>1599808</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la calidad percibida del medioambiente de su barrio en 2023</t>
+          <t>Población según la calidad percibida del medioambiente de su barrio en 2023 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,82 +9625,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11446</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>18077</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4865</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1835</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10966</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>18642</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22187</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>37263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62506</t>
+          <t>63557</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60581</t>
+          <t>59780</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85617</t>
+          <t>87864</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103808</t>
+          <t>104588</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>138812</t>
+          <t>140614</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>294204</t>
+          <t>295871</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>333932</t>
+          <t>335820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>483970</t>
+          <t>481296</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>521332</t>
+          <t>521365</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>789857</t>
+          <t>790672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>846466</t>
+          <t>848870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118980</t>
+          <t>118435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155416</t>
+          <t>155078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149425</t>
+          <t>149018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181997</t>
+          <t>182827</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276052</t>
+          <t>274290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325546</t>
+          <t>325221</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,47 +10342,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>6237</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>13747</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>6237</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>13288</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>19551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26760</t>
+          <t>27877</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40496</t>
+          <t>41149</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95316</t>
+          <t>101173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>179819</t>
+          <t>178716</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118134</t>
+          <t>118225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>195909</t>
+          <t>199058</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>244883</t>
+          <t>248799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>358364</t>
+          <t>358284</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1647130</t>
+          <t>1646452</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1912699</t>
+          <t>1881270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,82 +10646,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>71,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>82,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1672477</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1575173</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1821167</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>74,82%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>70,46%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>81,47%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3667</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>3405475</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>3255751</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3629061</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>75,27%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>71,96%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>83,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2162</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1672477</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1576281</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1837548</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>74,82%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>70,51%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>82,2%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3667</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3405475</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>3253450</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3607881</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>75,27%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>269813</t>
+          <t>288082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>462065</t>
+          <t>463203</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273927</t>
+          <t>283714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465138</t>
+          <t>464984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>628976</t>
+          <t>630313</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>892431</t>
+          <t>906503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29681</t>
+          <t>30471</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40890</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69944</t>
+          <t>73246</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48710</t>
+          <t>50066</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76118</t>
+          <t>77026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>97548</t>
+          <t>95903</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>139005</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>434205</t>
+          <t>433654</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>484043</t>
+          <t>481815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>447181</t>
+          <t>446562</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>488110</t>
+          <t>487753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>891295</t>
+          <t>891878</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>958873</t>
+          <t>955634</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99314</t>
+          <t>99343</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143022</t>
+          <t>141733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>100115</t>
+          <t>101017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134548</t>
+          <t>133669</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>210450</t>
+          <t>213165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>266730</t>
+          <t>270812</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,49 +11671,49 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>10655</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>5831</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>18830</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>10655</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>5921</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>18747</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>25</t>
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29613</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17861</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41859</t>
+          <t>41285</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45859</t>
+          <t>47059</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48912</t>
+          <t>48727</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83104</t>
+          <t>82367</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>191546</t>
+          <t>194621</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>287487</t>
+          <t>286664</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>240762</t>
+          <t>244178</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>334274</t>
+          <t>331227</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>467745</t>
+          <t>478214</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>603380</t>
+          <t>607401</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2412911</t>
+          <t>2408414</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2724648</t>
+          <t>2714123</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,47 +12010,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>69,88%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>78,75%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3810</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2644332</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2552324</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2814546</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>72,54%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>70,01%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>79,05%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3810</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2644332</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2545111</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2816427</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>72,54%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>69,81%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4999823</t>
+          <t>5000765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5394822</t>
+          <t>5374411</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>506270</t>
+          <t>508546</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>727759</t>
+          <t>730773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>558281</t>
+          <t>559544</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>750087</t>
+          <t>743768</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1146123</t>
+          <t>1170271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1438260</t>
+          <t>1438077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P05B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05B-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>15643</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19991</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41127</t>
+          <t>40917</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47590</t>
+          <t>48051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78304</t>
+          <t>76856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>74371</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110555</t>
+          <t>112601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199298</t>
+          <t>200437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>251943</t>
+          <t>253362</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>246669</t>
+          <t>246560</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310512</t>
+          <t>308135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>462713</t>
+          <t>460456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>541486</t>
+          <t>541501</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>639619</t>
+          <t>636799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>700476</t>
+          <t>698369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>819859</t>
+          <t>825364</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>893300</t>
+          <t>892533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1487675</t>
+          <t>1482403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1573863</t>
+          <t>1574791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86158</t>
+          <t>86134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122766</t>
+          <t>124218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91866</t>
+          <t>93016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>133392</t>
+          <t>133273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186232</t>
+          <t>188318</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>244538</t>
+          <t>244214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22378</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33483</t>
+          <t>34764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>24272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48595</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46910</t>
+          <t>46452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78321</t>
+          <t>75853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76457</t>
+          <t>76966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113079</t>
+          <t>116461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283056</t>
+          <t>282767</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>348206</t>
+          <t>348491</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>302435</t>
+          <t>302163</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>366812</t>
+          <t>368459</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>602581</t>
+          <t>600973</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>694114</t>
+          <t>694243</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1116084</t>
+          <t>1114261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1191417</t>
+          <t>1196681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>981026</t>
+          <t>975412</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1057475</t>
+          <t>1055344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2115352</t>
+          <t>2111122</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2226483</t>
+          <t>2223487</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150481</t>
+          <t>150867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201062</t>
+          <t>201414</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143007</t>
+          <t>143679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193298</t>
+          <t>192674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307956</t>
+          <t>302950</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>376809</t>
+          <t>374949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>12286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>38788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>105512</t>
+          <t>104800</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148818</t>
+          <t>145974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80015</t>
+          <t>80561</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>117297</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>194522</t>
+          <t>196288</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>247059</t>
+          <t>248735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>305672</t>
+          <t>308662</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>353628</t>
+          <t>354690</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>288430</t>
+          <t>289239</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>332395</t>
+          <t>331632</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>612477</t>
+          <t>613095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>676181</t>
+          <t>672463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62098</t>
+          <t>61605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94335</t>
+          <t>95357</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60492</t>
+          <t>63052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105249</t>
+          <t>103177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>149036</t>
+          <t>146515</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32611</t>
+          <t>33738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30041</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58166</t>
+          <t>56316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58566</t>
+          <t>60476</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95655</t>
+          <t>95098</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116553</t>
+          <t>115043</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>160354</t>
+          <t>163137</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>185225</t>
+          <t>185308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243605</t>
+          <t>242265</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621924</t>
+          <t>618840</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>712896</t>
+          <t>709068</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>657519</t>
+          <t>659971</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>752487</t>
+          <t>750993</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1304224</t>
+          <t>1306335</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1437931</t>
+          <t>1433301</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2098637</t>
+          <t>2102092</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2206359</t>
+          <t>2209529</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2135263</t>
+          <t>2132902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2246005</t>
+          <t>2245206</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4267314</t>
+          <t>4268385</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4424225</t>
+          <t>4424624</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>318544</t>
+          <t>323105</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>391800</t>
+          <t>391780</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>293614</t>
+          <t>295168</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>361689</t>
+          <t>364175</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>635306</t>
+          <t>633860</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>733809</t>
+          <t>734071</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36010</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114121</t>
+          <t>115455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>160337</t>
+          <t>160897</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>177583</t>
+          <t>181396</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>231226</t>
+          <t>235212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>309620</t>
+          <t>309021</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>380172</t>
+          <t>377363</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>697645</t>
+          <t>697036</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>754530</t>
+          <t>752995</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>944799</t>
+          <t>948821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1009726</t>
+          <t>1012612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1664835</t>
+          <t>1663704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1750506</t>
+          <t>1751264</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,21%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75997</t>
+          <t>76054</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113269</t>
+          <t>113691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103301</t>
+          <t>105215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>148081</t>
+          <t>147965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>190501</t>
+          <t>191686</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248165</t>
+          <t>248584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36372</t>
+          <t>35904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44745</t>
+          <t>44261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39736</t>
+          <t>41205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72739</t>
+          <t>72155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>238154</t>
+          <t>236919</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>298300</t>
+          <t>297689</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>232770</t>
+          <t>235458</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>299190</t>
+          <t>295852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>485582</t>
+          <t>486547</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>577689</t>
+          <t>577418</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1393351</t>
+          <t>1389888</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1471606</t>
+          <t>1472749</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1236847</t>
+          <t>1232821</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1314770</t>
+          <t>1312911</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2655024</t>
+          <t>2650820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2764991</t>
+          <t>2762027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198037</t>
+          <t>199874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>256993</t>
+          <t>255953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>153267</t>
+          <t>153874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205153</t>
+          <t>202092</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>365331</t>
+          <t>367804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>441908</t>
+          <t>443878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48035</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78573</t>
+          <t>79552</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>60057</t>
+          <t>59329</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93243</t>
+          <t>93330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115413</t>
+          <t>115257</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161621</t>
+          <t>161553</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>318553</t>
+          <t>320111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>361453</t>
+          <t>363556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>294276</t>
+          <t>293691</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>334601</t>
+          <t>335616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>627388</t>
+          <t>625363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>686727</t>
+          <t>685225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48221</t>
+          <t>47854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79576</t>
+          <t>79661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49716</t>
+          <t>49783</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82234</t>
+          <t>80221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103131</t>
+          <t>105316</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148964</t>
+          <t>148817</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24814</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>36781</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58208</t>
+          <t>57518</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34010</t>
+          <t>35631</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63296</t>
+          <t>64063</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72492</t>
+          <t>71567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112267</t>
+          <t>112286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>427257</t>
+          <t>424753</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>511713</t>
+          <t>506662</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>502678</t>
+          <t>501567</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>588502</t>
+          <t>589863</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>953818</t>
+          <t>954894</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1075288</t>
+          <t>1068194</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2447027</t>
+          <t>2448186</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2553742</t>
+          <t>2554085</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2516961</t>
+          <t>2512933</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2621762</t>
+          <t>2625735</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4995387</t>
+          <t>4984681</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5142852</t>
+          <t>5140765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>345962</t>
+          <t>345591</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>424890</t>
+          <t>418716</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>329593</t>
+          <t>328423</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>401985</t>
+          <t>403107</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>695716</t>
+          <t>697692</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>801385</t>
+          <t>802287</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15025</t>
+          <t>15092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35668</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21476</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73477</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110141</t>
+          <t>110790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107348</t>
+          <t>104949</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>154946</t>
+          <t>149728</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>189861</t>
+          <t>189973</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>246087</t>
+          <t>245573</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>437339</t>
+          <t>435014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>488368</t>
+          <t>490432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>598301</t>
+          <t>594206</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>661010</t>
+          <t>657011</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1052866</t>
+          <t>1050469</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1129421</t>
+          <t>1132518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,07%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168472</t>
+          <t>166823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213045</t>
+          <t>213456</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>183185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235336</t>
+          <t>236143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>361810</t>
+          <t>363638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>428881</t>
+          <t>435439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>22807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>30927</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25999</t>
+          <t>26364</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51910</t>
+          <t>50190</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43652</t>
+          <t>42829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75951</t>
+          <t>74758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>228113</t>
+          <t>229585</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>290227</t>
+          <t>292683</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222369</t>
+          <t>226048</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>284931</t>
+          <t>288947</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>471348</t>
+          <t>472525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>558093</t>
+          <t>559654</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1297743</t>
+          <t>1305510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1389962</t>
+          <t>1391214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1194550</t>
+          <t>1194440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1279469</t>
+          <t>1284382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2509979</t>
+          <t>2520226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2640349</t>
+          <t>2647990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,36%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>397613</t>
+          <t>402924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>474442</t>
+          <t>474508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>410885</t>
+          <t>410587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>487249</t>
+          <t>488077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>833166</t>
+          <t>835754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>935646</t>
+          <t>947422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24219</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48931</t>
+          <t>48851</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81633</t>
+          <t>80889</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50146</t>
+          <t>50870</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81154</t>
+          <t>80722</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108125</t>
+          <t>107818</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>152899</t>
+          <t>154363</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>327424</t>
+          <t>326430</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>372960</t>
+          <t>374157</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>332873</t>
+          <t>332460</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>375937</t>
+          <t>375680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>670143</t>
+          <t>672033</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>736220</t>
+          <t>735595</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105330</t>
+          <t>104257</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>146979</t>
+          <t>145316</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>104874</t>
+          <t>103290</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142693</t>
+          <t>141527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>222782</t>
+          <t>218953</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>279144</t>
+          <t>274008</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>19734</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29252</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>23160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48203</t>
+          <t>48101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53132</t>
+          <t>54009</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87148</t>
+          <t>88327</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>84041</t>
+          <t>85290</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>123217</t>
+          <t>125510</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>381081</t>
+          <t>378555</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>456629</t>
+          <t>455311</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>405501</t>
+          <t>405303</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>485514</t>
+          <t>483547</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>804634</t>
+          <t>804112</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>917072</t>
+          <t>916767</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2102274</t>
+          <t>2098812</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2211854</t>
+          <t>2211101</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2160856</t>
+          <t>2155521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2285398</t>
+          <t>2276592</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4292259</t>
+          <t>4292975</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4454957</t>
+          <t>4459156</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,75%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>703169</t>
+          <t>707040</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>797776</t>
+          <t>801662</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>728211</t>
+          <t>728105</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>830912</t>
+          <t>831616</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1452110</t>
+          <t>1456076</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1599808</t>
+          <t>1602953</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12891</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,67 +9753,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>13664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>15004</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>9471</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>23553</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>14853</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>9405</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>21967</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48928</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37263</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63557</t>
+          <t>65764</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>71410</t>
+          <t>77980</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59780</t>
+          <t>65110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>93759</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>120338</t>
+          <t>128772</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104588</t>
+          <t>110114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>140614</t>
+          <t>148430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>315076</t>
+          <t>351277</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>295871</t>
+          <t>330185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>335820</t>
+          <t>376380</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>502948</t>
+          <t>548621</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>481296</t>
+          <t>526823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>521365</t>
+          <t>570397</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>818024</t>
+          <t>899898</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>790672</t>
+          <t>870194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>848870</t>
+          <t>928282</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>136191</t>
+          <t>160420</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118435</t>
+          <t>138324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155078</t>
+          <t>181892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>164782</t>
+          <t>178518</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149018</t>
+          <t>161460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182827</t>
+          <t>195176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>300973</t>
+          <t>338939</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>274290</t>
+          <t>312905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325221</t>
+          <t>367324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>512328</t>
+          <t>574403</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>512328</t>
+          <t>574403</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>512328</t>
+          <t>574403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>752128</t>
+          <t>818418</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>752128</t>
+          <t>818418</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>752128</t>
+          <t>818418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1264456</t>
+          <t>1392821</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1264456</t>
+          <t>1392821</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1264456</t>
+          <t>1392821</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8416</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,17 +10357,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19551</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>28150</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>40872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>144327</t>
+          <t>156276</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101173</t>
+          <t>129869</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>178716</t>
+          <t>186975</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>163593</t>
+          <t>182380</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>118225</t>
+          <t>161259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>199058</t>
+          <t>210714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>307920</t>
+          <t>338656</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>248799</t>
+          <t>303166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>358284</t>
+          <t>376271</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1732998</t>
+          <t>1629120</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1581390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1881270</t>
+          <t>1679908</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1672477</t>
+          <t>1580257</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1575173</t>
+          <t>1540140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1821167</t>
+          <t>1617956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3405475</t>
+          <t>3209377</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3255751</t>
+          <t>3146195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3629061</t>
+          <t>3277353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>398353</t>
+          <t>430721</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288082</t>
+          <t>384861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>463203</t>
+          <t>473070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>378367</t>
+          <t>383645</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283714</t>
+          <t>351669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>464984</t>
+          <t>417508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>776720</t>
+          <t>814365</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>630313</t>
+          <t>755780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>906503</t>
+          <t>873544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2289090</t>
+          <t>2229262</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2289090</t>
+          <t>2229262</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2289090</t>
+          <t>2229262</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2235412</t>
+          <t>2168375</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2235412</t>
+          <t>2168375</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2235412</t>
+          <t>2168375</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4524502</t>
+          <t>4397637</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4524502</t>
+          <t>4397637</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4524502</t>
+          <t>4397637</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,22 +11039,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>13946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54644</t>
+          <t>60020</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41631</t>
+          <t>46272</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73246</t>
+          <t>79976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61531</t>
+          <t>70340</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50066</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77026</t>
+          <t>86627</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>116176</t>
+          <t>130359</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>95903</t>
+          <t>109532</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>135677</t>
+          <t>152098</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>458505</t>
+          <t>497809</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>433654</t>
+          <t>470639</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>481815</t>
+          <t>521886</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>468908</t>
+          <t>519259</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>446562</t>
+          <t>498043</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>487753</t>
+          <t>540292</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>927413</t>
+          <t>1017069</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>891878</t>
+          <t>984799</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>955634</t>
+          <t>1053393</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -11421,64 +11421,64 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>120398</t>
+          <t>139512</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99343</t>
+          <t>117330</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141733</t>
+          <t>164142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>23,11%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>130457</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>112804</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>148733</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>17,82%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>15,4%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>116158</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>101017</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>133669</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
           <t>20,31%</t>
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>236556</t>
+          <t>269969</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>213165</t>
+          <t>240296</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>270812</t>
+          <t>299308</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>645167</t>
+          <t>710151</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>645167</t>
+          <t>710151</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>645167</t>
+          <t>710151</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>658049</t>
+          <t>732267</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>658049</t>
+          <t>732267</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>658049</t>
+          <t>732267</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1303216</t>
+          <t>1442418</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1303216</t>
+          <t>1442418</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1303216</t>
+          <t>1442418</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,94 +11651,94 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>10892</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>6186</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>18090</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>20215</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>12845</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>30438</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>10655</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>5831</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>18830</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>20180</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>12815</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>31374</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>27640</t>
+          <t>28545</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>19251</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41285</t>
+          <t>42849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>34759</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>27844</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47059</t>
+          <t>50077</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,27 +11834,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>62399</t>
+          <t>65257</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48727</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82367</t>
+          <t>83694</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>247899</t>
+          <t>267088</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194621</t>
+          <t>236015</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>286664</t>
+          <t>304871</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>296535</t>
+          <t>330699</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>244178</t>
+          <t>297814</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>331227</t>
+          <t>362649</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>544434</t>
+          <t>597787</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>478214</t>
+          <t>553024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>607401</t>
+          <t>652929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2506580</t>
+          <t>2478206</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2408414</t>
+          <t>2418391</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2714123</t>
+          <t>2538728</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,22 +12025,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2644332</t>
+          <t>2648136</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2552324</t>
+          <t>2603623</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2814546</t>
+          <t>2699496</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5150912</t>
+          <t>5126342</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5000765</t>
+          <t>5045202</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5374411</t>
+          <t>5198674</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>654942</t>
+          <t>730653</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>508546</t>
+          <t>675850</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>730773</t>
+          <t>788285</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>659307</t>
+          <t>692619</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>559544</t>
+          <t>651738</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>743768</t>
+          <t>735513</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1314249</t>
+          <t>1423272</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1170271</t>
+          <t>1355002</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1438077</t>
+          <t>1491091</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3446586</t>
+          <t>3513816</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3446586</t>
+          <t>3513816</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3446586</t>
+          <t>3513816</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3645588</t>
+          <t>3719059</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3645588</t>
+          <t>3719059</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3645588</t>
+          <t>3719059</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7092174</t>
+          <t>7232875</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7092174</t>
+          <t>7232875</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7092174</t>
+          <t>7232875</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
